--- a/data/location-labels.xlsx
+++ b/data/location-labels.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F119"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,27 +421,2367 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>B</v>
+        <v>G</v>
       </c>
       <c r="B2">
+        <v>39</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>G390101</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>G</v>
+      </c>
+      <c r="B3">
+        <v>39</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>G390102</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>G</v>
+      </c>
+      <c r="B4">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>G390103</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>G</v>
+      </c>
+      <c r="B5">
+        <v>39</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
+        <v>G390201</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>G</v>
+      </c>
+      <c r="B6">
+        <v>39</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="str">
+        <v>G390202</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>G</v>
+      </c>
+      <c r="B7">
+        <v>39</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="str">
+        <v>G390203</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>G</v>
+      </c>
+      <c r="B8">
+        <v>39</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <v>G390204</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>G</v>
+      </c>
+      <c r="B9">
+        <v>39</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
+        <v>G390301</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>G</v>
+      </c>
+      <c r="B10">
+        <v>39</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="str">
+        <v>G390302</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>G</v>
+      </c>
+      <c r="B11">
+        <v>39</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="str">
+        <v>G390303</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>G</v>
+      </c>
+      <c r="B12">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="str">
+        <v>G390304</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>G</v>
+      </c>
+      <c r="B13">
+        <v>39</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="str">
+        <v>G390401</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>G</v>
+      </c>
+      <c r="B14">
+        <v>39</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="str">
+        <v>G390402</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>G</v>
+      </c>
+      <c r="B15">
+        <v>40</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="str">
+        <v>G400101</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>G</v>
+      </c>
+      <c r="B16">
+        <v>40</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" t="str">
+        <v>G400102</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>G</v>
+      </c>
+      <c r="B17">
+        <v>40</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="str">
+        <v>G400103</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>G</v>
+      </c>
+      <c r="B18">
+        <v>40</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" t="str">
+        <v>G400104</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>G</v>
+      </c>
+      <c r="B19">
+        <v>40</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19" t="str">
+        <v>G400105</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>G</v>
+      </c>
+      <c r="B20">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="str">
+        <v>G400201</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>G</v>
+      </c>
+      <c r="B21">
+        <v>40</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="str">
+        <v>G400202</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>G</v>
+      </c>
+      <c r="B22">
+        <v>40</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22" t="str">
+        <v>G400203</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>G</v>
+      </c>
+      <c r="B23">
+        <v>40</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" t="str">
+        <v>G400204</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>G</v>
+      </c>
+      <c r="B24">
+        <v>40</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24" t="str">
+        <v>G400205</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>G</v>
+      </c>
+      <c r="B25">
+        <v>40</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25" t="str">
+        <v>G400206</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>G</v>
+      </c>
+      <c r="B26">
+        <v>40</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="str">
+        <v>G400301</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>G</v>
+      </c>
+      <c r="B27">
+        <v>40</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="str">
+        <v>G400302</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>G</v>
+      </c>
+      <c r="B28">
+        <v>40</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="str">
+        <v>G400303</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>G</v>
+      </c>
+      <c r="B29">
+        <v>40</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" t="str">
+        <v>G400304</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>G</v>
+      </c>
+      <c r="B30">
+        <v>40</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30" t="str">
+        <v>G400305</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>G</v>
+      </c>
+      <c r="B31">
+        <v>40</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="str">
+        <v>G400401</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>G</v>
+      </c>
+      <c r="B32">
+        <v>40</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="str">
+        <v>G400402</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>G</v>
+      </c>
+      <c r="B33">
+        <v>40</v>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33" t="str">
+        <v>G400403</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>G</v>
+      </c>
+      <c r="B34">
+        <v>40</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34" t="str">
+        <v>G400404</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>G</v>
+      </c>
+      <c r="B35">
+        <v>41</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="str">
+        <v>G410101</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>G</v>
+      </c>
+      <c r="B36">
+        <v>41</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36" t="str">
+        <v>G410102</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>G</v>
+      </c>
+      <c r="B37">
+        <v>41</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" t="str">
+        <v>G410103</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>G</v>
+      </c>
+      <c r="B38">
+        <v>41</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38" t="str">
+        <v>G410104</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>G</v>
+      </c>
+      <c r="B39">
+        <v>41</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>5</v>
+      </c>
+      <c r="E39" t="str">
+        <v>G410105</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>G</v>
+      </c>
+      <c r="B40">
+        <v>41</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="str">
+        <v>G410201</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>G</v>
+      </c>
+      <c r="B41">
+        <v>41</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41" t="str">
+        <v>G410202</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>G</v>
+      </c>
+      <c r="B42">
+        <v>41</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42" t="str">
+        <v>G410203</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>G</v>
+      </c>
+      <c r="B43">
+        <v>41</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43" t="str">
+        <v>G410204</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>G</v>
+      </c>
+      <c r="B44">
+        <v>41</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+      <c r="E44" t="str">
+        <v>G410205</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>G</v>
+      </c>
+      <c r="B45">
+        <v>41</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="str">
+        <v>G410301</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>G</v>
+      </c>
+      <c r="B46">
+        <v>41</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46" t="str">
+        <v>G410302</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>G</v>
+      </c>
+      <c r="B47">
+        <v>41</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47" t="str">
+        <v>G410303</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>G</v>
+      </c>
+      <c r="B48">
+        <v>41</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="str">
+        <v>G410401</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>G</v>
+      </c>
+      <c r="B49">
+        <v>41</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49" t="str">
+        <v>G410402</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>G</v>
+      </c>
+      <c r="B50">
+        <v>41</v>
+      </c>
+      <c r="C50">
+        <v>4</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50" t="str">
+        <v>G410403</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>G</v>
+      </c>
+      <c r="B51">
+        <v>41</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51">
+        <v>4</v>
+      </c>
+      <c r="E51" t="str">
+        <v>G410404</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>G</v>
+      </c>
+      <c r="B52">
+        <v>42</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" t="str">
+        <v>G420101</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>G</v>
+      </c>
+      <c r="B53">
+        <v>42</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>2</v>
+      </c>
+      <c r="E53" t="str">
+        <v>G420102</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>G</v>
+      </c>
+      <c r="B54">
+        <v>42</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54" t="str">
+        <v>G420103</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>G</v>
+      </c>
+      <c r="B55">
+        <v>42</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55" t="str">
+        <v>G420104</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>G</v>
+      </c>
+      <c r="B56">
+        <v>42</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+      <c r="E56" t="str">
+        <v>G420105</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>G</v>
+      </c>
+      <c r="B57">
+        <v>42</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>6</v>
+      </c>
+      <c r="E57" t="str">
+        <v>G420106</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>G</v>
+      </c>
+      <c r="B58">
+        <v>42</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
         <v>7</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>99</v>
-      </c>
-      <c r="E2" t="str">
-        <v>B070199</v>
-      </c>
-      <c r="F2">
+      <c r="E58" t="str">
+        <v>G420107</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>G</v>
+      </c>
+      <c r="B59">
+        <v>42</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="str">
+        <v>G420201</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>G</v>
+      </c>
+      <c r="B60">
+        <v>42</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>2</v>
+      </c>
+      <c r="E60" t="str">
+        <v>G420202</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>G</v>
+      </c>
+      <c r="B61">
+        <v>42</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61" t="str">
+        <v>G420203</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>G</v>
+      </c>
+      <c r="B62">
+        <v>42</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62" t="str">
+        <v>G420204</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>G</v>
+      </c>
+      <c r="B63">
+        <v>42</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+      <c r="E63" t="str">
+        <v>G420205</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>G</v>
+      </c>
+      <c r="B64">
+        <v>42</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64" t="str">
+        <v>G420301</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>G</v>
+      </c>
+      <c r="B65">
+        <v>42</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65" t="str">
+        <v>G420302</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>G</v>
+      </c>
+      <c r="B66">
+        <v>42</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+      <c r="D66">
+        <v>3</v>
+      </c>
+      <c r="E66" t="str">
+        <v>G420303</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>G</v>
+      </c>
+      <c r="B67">
+        <v>42</v>
+      </c>
+      <c r="C67">
+        <v>4</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" t="str">
+        <v>G420401</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>G</v>
+      </c>
+      <c r="B68">
+        <v>42</v>
+      </c>
+      <c r="C68">
+        <v>4</v>
+      </c>
+      <c r="D68">
+        <v>2</v>
+      </c>
+      <c r="E68" t="str">
+        <v>G420402</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>G</v>
+      </c>
+      <c r="B69">
+        <v>42</v>
+      </c>
+      <c r="C69">
+        <v>4</v>
+      </c>
+      <c r="D69">
+        <v>3</v>
+      </c>
+      <c r="E69" t="str">
+        <v>G420403</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>G</v>
+      </c>
+      <c r="B70">
+        <v>42</v>
+      </c>
+      <c r="C70">
+        <v>4</v>
+      </c>
+      <c r="D70">
+        <v>4</v>
+      </c>
+      <c r="E70" t="str">
+        <v>G420404</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>G</v>
+      </c>
+      <c r="B71">
+        <v>43</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" t="str">
+        <v>G430101</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>G</v>
+      </c>
+      <c r="B72">
+        <v>43</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72" t="str">
+        <v>G430102</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>G</v>
+      </c>
+      <c r="B73">
+        <v>43</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73" t="str">
+        <v>G430103</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>G</v>
+      </c>
+      <c r="B74">
+        <v>43</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74" t="str">
+        <v>G430104</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>G</v>
+      </c>
+      <c r="B75">
+        <v>43</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>5</v>
+      </c>
+      <c r="E75" t="str">
+        <v>G430105</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>G</v>
+      </c>
+      <c r="B76">
+        <v>43</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>6</v>
+      </c>
+      <c r="E76" t="str">
+        <v>G430106</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>G</v>
+      </c>
+      <c r="B77">
+        <v>43</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77" t="str">
+        <v>G430201</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>G</v>
+      </c>
+      <c r="B78">
+        <v>43</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+      <c r="E78" t="str">
+        <v>G430202</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>G</v>
+      </c>
+      <c r="B79">
+        <v>43</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>3</v>
+      </c>
+      <c r="E79" t="str">
+        <v>G430203</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>G</v>
+      </c>
+      <c r="B80">
+        <v>43</v>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80" t="str">
+        <v>G430204</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>G</v>
+      </c>
+      <c r="B81">
+        <v>43</v>
+      </c>
+      <c r="C81">
+        <v>3</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81" t="str">
+        <v>G430301</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>G</v>
+      </c>
+      <c r="B82">
+        <v>43</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82" t="str">
+        <v>G430302</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>G</v>
+      </c>
+      <c r="B83">
+        <v>43</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83">
+        <v>3</v>
+      </c>
+      <c r="E83" t="str">
+        <v>G430303</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>G</v>
+      </c>
+      <c r="B84">
+        <v>43</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84">
+        <v>4</v>
+      </c>
+      <c r="E84" t="str">
+        <v>G430304</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>G</v>
+      </c>
+      <c r="B85">
+        <v>43</v>
+      </c>
+      <c r="C85">
+        <v>3</v>
+      </c>
+      <c r="D85">
+        <v>5</v>
+      </c>
+      <c r="E85" t="str">
+        <v>G430305</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>G</v>
+      </c>
+      <c r="B86">
+        <v>43</v>
+      </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="D86">
+        <v>6</v>
+      </c>
+      <c r="E86" t="str">
+        <v>G430306</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>G</v>
+      </c>
+      <c r="B87">
+        <v>43</v>
+      </c>
+      <c r="C87">
+        <v>4</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87" t="str">
+        <v>G430401</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>G</v>
+      </c>
+      <c r="B88">
+        <v>43</v>
+      </c>
+      <c r="C88">
+        <v>4</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88" t="str">
+        <v>G430402</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>G</v>
+      </c>
+      <c r="B89">
+        <v>43</v>
+      </c>
+      <c r="C89">
+        <v>4</v>
+      </c>
+      <c r="D89">
+        <v>3</v>
+      </c>
+      <c r="E89" t="str">
+        <v>G430403</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>G</v>
+      </c>
+      <c r="B90">
+        <v>43</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90">
+        <v>4</v>
+      </c>
+      <c r="E90" t="str">
+        <v>G430404</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>G</v>
+      </c>
+      <c r="B91">
+        <v>43</v>
+      </c>
+      <c r="C91">
+        <v>4</v>
+      </c>
+      <c r="D91">
+        <v>5</v>
+      </c>
+      <c r="E91" t="str">
+        <v>G430405</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>G</v>
+      </c>
+      <c r="B92">
+        <v>44</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92" t="str">
+        <v>G440101</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>G</v>
+      </c>
+      <c r="B93">
+        <v>44</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93">
+        <v>2</v>
+      </c>
+      <c r="E93" t="str">
+        <v>G440102</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>G</v>
+      </c>
+      <c r="B94">
+        <v>44</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94" t="str">
+        <v>G440201</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>G</v>
+      </c>
+      <c r="B95">
+        <v>44</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95">
+        <v>2</v>
+      </c>
+      <c r="E95" t="str">
+        <v>G440202</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>G</v>
+      </c>
+      <c r="B96">
+        <v>44</v>
+      </c>
+      <c r="C96">
+        <v>3</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96" t="str">
+        <v>G440301</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>G</v>
+      </c>
+      <c r="B97">
+        <v>45</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97" t="str">
+        <v>G450101</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>G</v>
+      </c>
+      <c r="B98">
+        <v>45</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98" t="str">
+        <v>G450201</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>G</v>
+      </c>
+      <c r="B99">
+        <v>45</v>
+      </c>
+      <c r="C99">
+        <v>3</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99" t="str">
+        <v>G450301</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>G</v>
+      </c>
+      <c r="B100">
+        <v>45</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+      <c r="E100" t="str">
+        <v>G450302</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>G</v>
+      </c>
+      <c r="B101">
+        <v>45</v>
+      </c>
+      <c r="C101">
+        <v>4</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101" t="str">
+        <v>G450401</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>G</v>
+      </c>
+      <c r="B102">
+        <v>45</v>
+      </c>
+      <c r="C102">
+        <v>4</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+      <c r="E102" t="str">
+        <v>G450402</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>G</v>
+      </c>
+      <c r="B103">
+        <v>45</v>
+      </c>
+      <c r="C103">
+        <v>4</v>
+      </c>
+      <c r="D103">
+        <v>3</v>
+      </c>
+      <c r="E103" t="str">
+        <v>G450403</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>G</v>
+      </c>
+      <c r="B104">
+        <v>45</v>
+      </c>
+      <c r="C104">
+        <v>4</v>
+      </c>
+      <c r="D104">
+        <v>4</v>
+      </c>
+      <c r="E104" t="str">
+        <v>G450404</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>G</v>
+      </c>
+      <c r="B105">
+        <v>45</v>
+      </c>
+      <c r="C105">
+        <v>5</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105" t="str">
+        <v>G450501</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>G</v>
+      </c>
+      <c r="B106">
+        <v>45</v>
+      </c>
+      <c r="C106">
+        <v>5</v>
+      </c>
+      <c r="D106">
+        <v>2</v>
+      </c>
+      <c r="E106" t="str">
+        <v>G450502</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>G</v>
+      </c>
+      <c r="B107">
+        <v>45</v>
+      </c>
+      <c r="C107">
+        <v>6</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107" t="str">
+        <v>G450601</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>G</v>
+      </c>
+      <c r="B108">
+        <v>45</v>
+      </c>
+      <c r="C108">
+        <v>6</v>
+      </c>
+      <c r="D108">
+        <v>2</v>
+      </c>
+      <c r="E108" t="str">
+        <v>G450602</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>G</v>
+      </c>
+      <c r="B109">
+        <v>45</v>
+      </c>
+      <c r="C109">
+        <v>6</v>
+      </c>
+      <c r="D109">
+        <v>3</v>
+      </c>
+      <c r="E109" t="str">
+        <v>G450603</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>G</v>
+      </c>
+      <c r="B110">
+        <v>45</v>
+      </c>
+      <c r="C110">
+        <v>6</v>
+      </c>
+      <c r="D110">
+        <v>4</v>
+      </c>
+      <c r="E110" t="str">
+        <v>G450604</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>G</v>
+      </c>
+      <c r="B111">
+        <v>45</v>
+      </c>
+      <c r="C111">
+        <v>6</v>
+      </c>
+      <c r="D111">
+        <v>5</v>
+      </c>
+      <c r="E111" t="str">
+        <v>G450605</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>G</v>
+      </c>
+      <c r="B112">
+        <v>45</v>
+      </c>
+      <c r="C112">
+        <v>6</v>
+      </c>
+      <c r="D112">
+        <v>6</v>
+      </c>
+      <c r="E112" t="str">
+        <v>G450606</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>G</v>
+      </c>
+      <c r="B113">
+        <v>45</v>
+      </c>
+      <c r="C113">
+        <v>6</v>
+      </c>
+      <c r="D113">
+        <v>7</v>
+      </c>
+      <c r="E113" t="str">
+        <v>G450607</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>G</v>
+      </c>
+      <c r="B114">
+        <v>45</v>
+      </c>
+      <c r="C114">
+        <v>6</v>
+      </c>
+      <c r="D114">
+        <v>8</v>
+      </c>
+      <c r="E114" t="str">
+        <v>G450608</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>G</v>
+      </c>
+      <c r="B115">
+        <v>45</v>
+      </c>
+      <c r="C115">
+        <v>6</v>
+      </c>
+      <c r="D115">
+        <v>9</v>
+      </c>
+      <c r="E115" t="str">
+        <v>G450609</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>G</v>
+      </c>
+      <c r="B116">
+        <v>45</v>
+      </c>
+      <c r="C116">
+        <v>6</v>
+      </c>
+      <c r="D116">
+        <v>10</v>
+      </c>
+      <c r="E116" t="str">
+        <v>G450610</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>G</v>
+      </c>
+      <c r="B117">
+        <v>45</v>
+      </c>
+      <c r="C117">
+        <v>6</v>
+      </c>
+      <c r="D117">
+        <v>11</v>
+      </c>
+      <c r="E117" t="str">
+        <v>G450611</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>G</v>
+      </c>
+      <c r="B118">
+        <v>45</v>
+      </c>
+      <c r="C118">
+        <v>6</v>
+      </c>
+      <c r="D118">
+        <v>12</v>
+      </c>
+      <c r="E118" t="str">
+        <v>G450612</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>G</v>
+      </c>
+      <c r="B119">
+        <v>45</v>
+      </c>
+      <c r="C119">
+        <v>6</v>
+      </c>
+      <c r="D119">
+        <v>13</v>
+      </c>
+      <c r="E119" t="str">
+        <v>G450613</v>
+      </c>
+      <c r="F119">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F119"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/location-labels.xlsx
+++ b/data/location-labels.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,421 +427,21 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E2" t="str">
-        <v>A010101</v>
+        <v>A010215</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>A</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="str">
-        <v>A010102</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>A</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" t="str">
-        <v>A010103</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>A</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5" t="str">
-        <v>A010104</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>A</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6" t="str">
-        <v>A010105</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>A</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7" t="str">
-        <v>A010106</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>A</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
-      <c r="E8" t="str">
-        <v>A010107</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>A</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
-      </c>
-      <c r="E9" t="str">
-        <v>A010108</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>A</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-      <c r="E10" t="str">
-        <v>A010109</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>A</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="str">
-        <v>A010301</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>A</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12" t="str">
-        <v>A010302</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>A</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>3</v>
-      </c>
-      <c r="E13" t="str">
-        <v>A010303</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>A</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14" t="str">
-        <v>A010304</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>A</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>5</v>
-      </c>
-      <c r="E15" t="str">
-        <v>A010305</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>A</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16">
-        <v>6</v>
-      </c>
-      <c r="E16" t="str">
-        <v>A010306</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>A</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17">
-        <v>7</v>
-      </c>
-      <c r="E17" t="str">
-        <v>A010307</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>A</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18">
-        <v>8</v>
-      </c>
-      <c r="E18" t="str">
-        <v>A010308</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>A</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19">
-        <v>9</v>
-      </c>
-      <c r="E19" t="str">
-        <v>A010309</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>A</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20">
-        <v>10</v>
-      </c>
-      <c r="E20" t="str">
-        <v>A010310</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>A</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21">
-        <v>11</v>
-      </c>
-      <c r="E21" t="str">
-        <v>A010311</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>A</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>12</v>
-      </c>
-      <c r="E22" t="str">
-        <v>A010312</v>
-      </c>
-      <c r="F22">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/location-labels.xlsx
+++ b/data/location-labels.xlsx
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>A</v>
+        <v>Z</v>
       </c>
       <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
       <c r="D2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E2" t="str">
-        <v>A010215</v>
+        <v>Z090109</v>
       </c>
       <c r="F2">
         <v>1</v>
